--- a/data/trans_dic/IP2002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les han extraído dientes por caries o por otro motivo</t>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,66</t>
+          <t>3,02; 9,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,55</t>
+          <t>2,71; 9,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 10,24</t>
+          <t>2,77; 10,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 9,05</t>
+          <t>2,33; 8,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 12,12</t>
+          <t>4,88; 12,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 13,72</t>
+          <t>5,4; 14,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,58</t>
+          <t>1,81; 7,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,63</t>
+          <t>1,48; 6,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 9,47</t>
+          <t>4,63; 9,7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,87</t>
+          <t>4,84; 9,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,47</t>
+          <t>2,81; 7,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,24</t>
+          <t>2,31; 6,52</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 11,71</t>
+          <t>5,5; 11,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,89</t>
+          <t>5,54; 12,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 10,46</t>
+          <t>4,85; 10,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 12,9</t>
+          <t>4,4; 11,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 12,33</t>
+          <t>5,99; 12,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,49</t>
+          <t>4,45; 10,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,17</t>
+          <t>3,57; 8,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,17</t>
+          <t>2,86; 8,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,73</t>
+          <t>6,65; 10,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,97</t>
+          <t>5,77; 10,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,37</t>
+          <t>4,74; 8,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,35</t>
+          <t>4,28; 8,55</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,13</t>
+          <t>3,41; 10,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,2</t>
+          <t>3,7; 10,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,72</t>
+          <t>1,88; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,49</t>
+          <t>2,58; 8,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,46</t>
+          <t>5,18; 12,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,02</t>
+          <t>4,65; 12,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,55</t>
+          <t>1,76; 6,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 11,9</t>
+          <t>4,1; 12,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 10,11</t>
+          <t>5,09; 10,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,64</t>
+          <t>4,85; 9,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,96</t>
+          <t>2,19; 5,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,77</t>
+          <t>3,75; 9,18</t>
         </is>
       </c>
     </row>
@@ -1136,52 +1137,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,67</t>
+          <t>4,64; 11,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,04</t>
+          <t>0,9; 5,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,42</t>
+          <t>4,63; 11,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,07</t>
+          <t>3,64; 10,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,49</t>
+          <t>2,69; 7,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,2</t>
+          <t>2,77; 8,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,78</t>
+          <t>3,24; 9,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 8,05</t>
+          <t>2,03; 8,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,49</t>
+          <t>4,36; 8,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,64</t>
+          <t>2,23; 5,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,53</t>
+          <t>3,19; 7,43</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,91</t>
+          <t>5,52; 8,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,99</t>
+          <t>4,13; 7,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,84</t>
+          <t>4,77; 7,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,6</t>
+          <t>4,46; 7,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 9,2</t>
+          <t>5,89; 9,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,66</t>
+          <t>5,41; 8,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,27</t>
+          <t>3,73; 6,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,7</t>
+          <t>3,73; 6,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,36</t>
+          <t>6,05; 8,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,39</t>
+          <t>5,23; 7,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,56</t>
+          <t>4,54; 6,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,73</t>
+          <t>4,43; 6,64</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les han extraído dientes por caries o por otro motivo (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6665</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6844</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12656</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4699</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18598</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19321</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12209</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3894; 12872</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3609; 12268</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3457; 12505</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2686; 10116</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7001; 17660</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7633; 19821</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2513; 11053</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2022; 9264</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12605; 26441</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>13291; 27330</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7407; 20489</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5814; 16410</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>15327</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16018</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13902</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14020</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17732</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>15044</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12131</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12437</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>33059</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31062</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>26032</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26457</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10222; 21615</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10601; 23300</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9388; 20862</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>8233; 21521</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12225; 24690</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9457; 21783</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7519; 18587</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7130; 20231</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>25937; 42507</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>23314; 40500</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>19166; 34333</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>18647; 37271</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7917</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9307</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11566</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11569</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5630</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13280</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>19483</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20876</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>11320</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>22280</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4461; 13310</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5358; 15218</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2787; 10306</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4857; 15448</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7212; 17575</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7086; 18342</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2826; 10940</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7526; 22273</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13737; 27188</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14399; 29561</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6773; 18355</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>13957; 34108</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15182</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4681</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14499</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10379</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9378</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10590</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>24559</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14096</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25089</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>17480</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>9261; 22306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1750; 9974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8912; 22286</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6046; 17112</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5328; 15023</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5432; 16927</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6172; 17631</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3609; 14379</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>17326; 33056</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>8701; 22143</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>17497; 34082</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>10971; 25546</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>45821</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36672</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40933</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38849</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>37518</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>95700</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>74649</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>76367</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>35622; 57038</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27367; 47763</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31401; 52486</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29229; 51005</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>40380; 61774</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>38044; 60920</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26153; 45040</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>27882; 50173</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>80403; 111998</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>71459; 101364</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>61774; 90001</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>62221; 93246</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,98</t>
+          <t>3,21; 10,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,21</t>
+          <t>2,6; 9,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,03</t>
+          <t>2,67; 10,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 8,79</t>
+          <t>2,26; 8,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,31</t>
+          <t>4,59; 12,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,4; 14,02</t>
+          <t>5,51; 13,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,95</t>
+          <t>1,56; 7,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,77</t>
+          <t>1,43; 6,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,7</t>
+          <t>4,65; 9,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,95</t>
+          <t>4,7; 10,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,77</t>
+          <t>2,87; 7,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,52</t>
+          <t>2,4; 6,62</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,63</t>
+          <t>5,76; 12,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 12,17</t>
+          <t>5,43; 11,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 10,78</t>
+          <t>4,65; 10,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,51</t>
+          <t>4,64; 11,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 12,09</t>
+          <t>6,0; 11,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 10,24</t>
+          <t>4,69; 10,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,82</t>
+          <t>3,45; 8,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,12</t>
+          <t>3,12; 8,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,9</t>
+          <t>6,29; 11,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 10,02</t>
+          <t>5,74; 10,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,49</t>
+          <t>4,63; 8,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,55</t>
+          <t>4,23; 8,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 10,18</t>
+          <t>3,29; 9,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,52</t>
+          <t>3,69; 10,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,96</t>
+          <t>1,74; 7,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,22</t>
+          <t>2,36; 8,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 12,61</t>
+          <t>5,24; 12,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 12,04</t>
+          <t>4,54; 11,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,82</t>
+          <t>1,64; 6,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 12,12</t>
+          <t>4,17; 11,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 10,07</t>
+          <t>5,06; 9,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,95</t>
+          <t>4,98; 9,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,95</t>
+          <t>2,16; 5,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,18</t>
+          <t>3,87; 8,73</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 11,18</t>
+          <t>4,7; 11,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,15</t>
+          <t>0,9; 5,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 11,58</t>
+          <t>4,58; 11,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 10,3</t>
+          <t>3,58; 10,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,59</t>
+          <t>2,76; 7,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,62</t>
+          <t>2,6; 8,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,25</t>
+          <t>3,27; 9,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,08</t>
+          <t>1,92; 7,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,32</t>
+          <t>4,46; 8,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,68</t>
+          <t>2,28; 5,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,89</t>
+          <t>4,74; 9,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,43</t>
+          <t>3,32; 7,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 8,84</t>
+          <t>5,64; 9,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,21</t>
+          <t>4,28; 7,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,97</t>
+          <t>4,73; 7,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,77</t>
+          <t>4,34; 7,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,02</t>
+          <t>5,87; 9,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,67</t>
+          <t>5,48; 8,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,43</t>
+          <t>3,61; 6,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,71</t>
+          <t>3,66; 6,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 8,42</t>
+          <t>6,12; 8,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,42</t>
+          <t>5,26; 7,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,62</t>
+          <t>4,51; 6,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,64</t>
+          <t>4,39; 6,6</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3894; 12872</t>
+          <t>4139; 13044</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3609; 12268</t>
+          <t>3458; 12775</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3457; 12505</t>
+          <t>3332; 12566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2686; 10116</t>
+          <t>2606; 10092</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7001; 17660</t>
+          <t>6585; 17350</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7633; 19821</t>
+          <t>7792; 19653</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2513; 11053</t>
+          <t>2170; 10836</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2022; 9264</t>
+          <t>1955; 9265</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12605; 26441</t>
+          <t>12670; 26884</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13291; 27330</t>
+          <t>12903; 28207</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7407; 20489</t>
+          <t>7576; 19115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5814; 16410</t>
+          <t>6054; 16667</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10222; 21615</t>
+          <t>10699; 22649</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10601; 23300</t>
+          <t>10409; 22697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9388; 20862</t>
+          <t>8996; 20197</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8233; 21521</t>
+          <t>8678; 22211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12225; 24690</t>
+          <t>12251; 24360</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9457; 21783</t>
+          <t>9985; 21836</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7519; 18587</t>
+          <t>7268; 18176</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7130; 20231</t>
+          <t>7783; 20780</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25937; 42507</t>
+          <t>24527; 43393</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23314; 40500</t>
+          <t>23214; 40886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19166; 34333</t>
+          <t>18714; 34364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18647; 37271</t>
+          <t>18460; 37366</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4461; 13310</t>
+          <t>4298; 12669</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5358; 15218</t>
+          <t>5341; 15335</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2787; 10306</t>
+          <t>2574; 10697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4857; 15448</t>
+          <t>4428; 15686</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7212; 17575</t>
+          <t>7300; 17981</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7086; 18342</t>
+          <t>6917; 17956</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2826; 10940</t>
+          <t>2627; 10947</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7526; 22273</t>
+          <t>7653; 21636</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13737; 27188</t>
+          <t>13655; 26656</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14399; 29561</t>
+          <t>14790; 28803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6773; 18355</t>
+          <t>6671; 17792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13957; 34108</t>
+          <t>14398; 32442</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9261; 22306</t>
+          <t>9384; 22750</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1750; 9974</t>
+          <t>1749; 10063</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8912; 22286</t>
+          <t>8811; 21840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6046; 17112</t>
+          <t>5939; 17085</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5328; 15023</t>
+          <t>5457; 15232</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5432; 16927</t>
+          <t>5103; 16118</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6172; 17631</t>
+          <t>6239; 17393</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3609; 14379</t>
+          <t>3420; 13760</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17326; 33056</t>
+          <t>17721; 33618</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8701; 22143</t>
+          <t>8873; 22526</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17497; 34082</t>
+          <t>18175; 35245</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10971; 25546</t>
+          <t>11416; 26244</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35622; 57038</t>
+          <t>36410; 58466</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27367; 47763</t>
+          <t>28359; 47592</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31401; 52486</t>
+          <t>31165; 52117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29229; 51005</t>
+          <t>28474; 50197</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40380; 61774</t>
+          <t>40242; 62884</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38044; 60920</t>
+          <t>38542; 60200</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26153; 45040</t>
+          <t>25286; 44593</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27882; 50173</t>
+          <t>27386; 49894</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80403; 111998</t>
+          <t>81343; 110831</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71459; 101364</t>
+          <t>71872; 103048</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61774; 90001</t>
+          <t>61321; 89220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>62221; 93246</t>
+          <t>61602; 92702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP2002-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,11</t>
+          <t>4,45; 12,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,59</t>
+          <t>5,54; 13,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,08</t>
+          <t>1,56; 7,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,77</t>
+          <t>1,34; 6,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 12,09</t>
+          <t>2,89; 9,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 13,9</t>
+          <t>2,6; 9,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,79</t>
+          <t>2,78; 10,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 6,77</t>
+          <t>2,36; 9,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,87</t>
+          <t>4,41; 9,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,27</t>
+          <t>4,81; 9,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,25</t>
+          <t>2,87; 7,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,62</t>
+          <t>2,38; 6,51</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,18%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 12,19</t>
+          <t>5,72; 12,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,85</t>
+          <t>4,73; 10,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 10,44</t>
+          <t>3,47; 9,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 11,88</t>
+          <t>2,98; 8,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,93</t>
+          <t>5,59; 11,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,26</t>
+          <t>5,38; 11,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,63</t>
+          <t>4,74; 10,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,34</t>
+          <t>4,34; 11,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,13</t>
+          <t>6,38; 10,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,11</t>
+          <t>5,64; 9,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,5</t>
+          <t>4,56; 8,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,57</t>
+          <t>4,1; 8,02</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,69</t>
+          <t>4,83; 12,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,6</t>
+          <t>4,6; 12,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,22</t>
+          <t>1,59; 6,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,34</t>
+          <t>4,01; 11,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,9</t>
+          <t>3,6; 10,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,79</t>
+          <t>3,59; 10,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,82</t>
+          <t>1,75; 6,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 11,78</t>
+          <t>3,28; 10,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,87</t>
+          <t>5,14; 10,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,7</t>
+          <t>4,96; 9,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,77</t>
+          <t>2,15; 5,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,73</t>
+          <t>4,49; 9,68</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,61%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,53%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,4</t>
+          <t>2,61; 7,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,2</t>
+          <t>2,47; 8,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,35</t>
+          <t>3,1; 8,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 10,29</t>
+          <t>1,87; 7,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,69</t>
+          <t>4,96; 11,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,21</t>
+          <t>1,13; 5,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 9,12</t>
+          <t>4,85; 11,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,74</t>
+          <t>3,65; 10,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,46</t>
+          <t>4,41; 8,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,78</t>
+          <t>2,18; 5,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,2</t>
+          <t>4,57; 8,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,63</t>
+          <t>3,25; 7,52</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,1%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,06</t>
+          <t>5,91; 9,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,18</t>
+          <t>5,35; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,91</t>
+          <t>3,63; 6,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,65</t>
+          <t>3,6; 6,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,18</t>
+          <t>5,56; 8,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,57</t>
+          <t>4,12; 6,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,36</t>
+          <t>4,76; 7,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,68</t>
+          <t>4,59; 7,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,33</t>
+          <t>6,16; 8,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,55</t>
+          <t>5,23; 7,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,56</t>
+          <t>4,55; 6,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,6</t>
+          <t>4,56; 6,81</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12656</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4181</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7395</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6665</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6844</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5451</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>11203</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12656</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>9986</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4139; 13044</t>
+          <t>6383; 17394</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3458; 12775</t>
+          <t>7829; 19395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3332; 12566</t>
+          <t>2174; 10541</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2606; 10092</t>
+          <t>1645; 8247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6585; 17350</t>
+          <t>3726; 12464</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7792; 19653</t>
+          <t>3463; 12714</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2170; 10836</t>
+          <t>3466; 12769</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1955; 9265</t>
+          <t>2810; 10856</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12670; 26884</t>
+          <t>12028; 25811</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12903; 28207</t>
+          <t>13200; 27099</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7576; 19115</t>
+          <t>7578; 19702</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6054; 16667</t>
+          <t>5765; 15772</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17732</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15044</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12131</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11705</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15327</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16018</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13902</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14020</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17732</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15044</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>24429</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10699; 22649</t>
+          <t>11675; 25187</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10409; 22697</t>
+          <t>10053; 22328</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8996; 20197</t>
+          <t>7312; 19309</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8678; 22211</t>
+          <t>6930; 19182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12251; 24360</t>
+          <t>10379; 21753</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9985; 21836</t>
+          <t>10297; 22770</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7268; 18176</t>
+          <t>9166; 20246</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7783; 20780</t>
+          <t>7887; 20492</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24527; 43393</t>
+          <t>24895; 41829</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23214; 40886</t>
+          <t>22808; 40308</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18714; 34364</t>
+          <t>18446; 33816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18460; 37366</t>
+          <t>16979; 33206</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11566</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11569</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5630</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12064</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7917</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9307</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5689</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>11566</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11569</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5630</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>21257</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4298; 12669</t>
+          <t>6726; 17368</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5341; 15335</t>
+          <t>6999; 18300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2574; 10697</t>
+          <t>2544; 10505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4428; 15686</t>
+          <t>6707; 19947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7300; 17981</t>
+          <t>4710; 13245</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6917; 17956</t>
+          <t>5191; 14758</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2627; 10947</t>
+          <t>2590; 9952</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7653; 21636</t>
+          <t>5074; 15566</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13655; 26656</t>
+          <t>13883; 27313</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14790; 28803</t>
+          <t>14735; 28637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6671; 17792</t>
+          <t>6627; 18388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14398; 32442</t>
+          <t>14438; 31168</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9378</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10590</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>15182</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4681</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>14499</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10379</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9378</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9414</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10590</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>16903</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9384; 22750</t>
+          <t>5169; 14830</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1749; 10063</t>
+          <t>4841; 16099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8811; 21840</t>
+          <t>5920; 16738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5939; 17085</t>
+          <t>3113; 13320</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5457; 15232</t>
+          <t>9904; 23274</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5103; 16118</t>
+          <t>2183; 9761</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6239; 17393</t>
+          <t>9337; 21979</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3420; 13760</t>
+          <t>6026; 16914</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17721; 33618</t>
+          <t>17538; 33757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8873; 22526</t>
+          <t>8511; 21972</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18175; 35245</t>
+          <t>17501; 34061</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11416; 26244</t>
+          <t>10772; 24960</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>45821</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>36672</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>40933</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38849</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>49879</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48684</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>72575</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36410; 58466</t>
+          <t>40464; 63034</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28359; 47592</t>
+          <t>37611; 60864</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31165; 52117</t>
+          <t>25408; 43923</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28474; 50197</t>
+          <t>24835; 46040</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40242; 62884</t>
+          <t>35874; 57442</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38542; 60200</t>
+          <t>27318; 46356</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25286; 44593</t>
+          <t>31333; 51664</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27386; 49894</t>
+          <t>28520; 49187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81343; 110831</t>
+          <t>81953; 111232</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71872; 103048</t>
+          <t>71434; 100916</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>61321; 89220</t>
+          <t>61818; 89187</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61602; 92702</t>
+          <t>59739; 89200</t>
         </is>
       </c>
     </row>
